--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/phi-4/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/phi-4/metrics_default_vs_simple.xlsx
@@ -420,22 +420,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.2706766917293233</v>
+        <v>0.2537313432835821</v>
       </c>
       <c r="B2">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2816901408450704</v>
+        <v>0.2605633802816901</v>
       </c>
       <c r="D2">
-        <v>0.7338129496402878</v>
+        <v>0.7553956834532374</v>
       </c>
       <c r="E2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>3</v>
